--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N31_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>29.25021376939929</v>
       </c>
       <c r="E2" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F2" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>26.78657332237608</v>
       </c>
       <c r="E3" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F3" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>30.42501940107115</v>
       </c>
       <c r="E4" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F4" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>4.143962822431028</v>
       </c>
       <c r="E5" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F5" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>7.226263826410507</v>
       </c>
       <c r="E6" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F6" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>20.40042184920182</v>
       </c>
       <c r="E7" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F7" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>21.69419152252939</v>
       </c>
       <c r="E8" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F8" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>16.516891121143</v>
       </c>
       <c r="E9" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F9" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>19.39077673076099</v>
       </c>
       <c r="E10" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F10" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         <v>23.44335918448138</v>
       </c>
       <c r="E11" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F11" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>33.39409029144316</v>
       </c>
       <c r="E12" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F12" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         <v>13.34140155484803</v>
       </c>
       <c r="E13" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F13" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>8.144225252538298</v>
       </c>
       <c r="E14" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F14" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
         <v>16.88897492592991</v>
       </c>
       <c r="E15" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F15" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         <v>12.40515343880981</v>
       </c>
       <c r="E16" t="n">
-        <v>9.250538162618136</v>
+        <v>8.964289098704377</v>
       </c>
       <c r="F16" t="n">
-        <v>8.546653135769962</v>
+        <v>8.379705862519438</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -945,6 +945,38 @@
         </is>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>W0014F0003T0006Z000C1N31.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>16.440885141984</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24.34542067338746</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8.964289098704377</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8.379705862519438</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>T5171</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>G4</t>
         </is>

--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.86002098251334</v>
+        <v>4.689753409658418</v>
       </c>
       <c r="D2" t="n">
-        <v>29.25021376939929</v>
+        <v>4.753159737527384</v>
       </c>
       <c r="E2" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F2" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.41197903269283</v>
+        <v>4.291946592812584</v>
       </c>
       <c r="D3" t="n">
-        <v>26.78657332237608</v>
+        <v>4.352818164886114</v>
       </c>
       <c r="E3" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F3" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.1081384346492</v>
+        <v>4.892572495630494</v>
       </c>
       <c r="D4" t="n">
-        <v>30.42501940107115</v>
+        <v>4.944065652674063</v>
       </c>
       <c r="E4" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F4" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.45841048755364</v>
+        <v>4.136991704227467</v>
       </c>
       <c r="D5" t="n">
-        <v>4.143962822431028</v>
+        <v>0.6733939586450421</v>
       </c>
       <c r="E5" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F5" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.030040718983992</v>
+        <v>1.142381616834899</v>
       </c>
       <c r="D6" t="n">
-        <v>7.226263826410507</v>
+        <v>1.174267871791707</v>
       </c>
       <c r="E6" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F6" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.8776687116036</v>
+        <v>5.017621165635585</v>
       </c>
       <c r="D7" t="n">
-        <v>20.40042184920182</v>
+        <v>3.315068550495295</v>
       </c>
       <c r="E7" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F7" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.59750809226676</v>
+        <v>4.484595064993349</v>
       </c>
       <c r="D8" t="n">
-        <v>21.69419152252939</v>
+        <v>3.525306122411026</v>
       </c>
       <c r="E8" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F8" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.48613158755632</v>
+        <v>2.678996382977901</v>
       </c>
       <c r="D9" t="n">
-        <v>16.516891121143</v>
+        <v>2.683994807185737</v>
       </c>
       <c r="E9" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F9" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>5.782751533812169</v>
+        <v>0.9396971242444775</v>
       </c>
       <c r="D10" t="n">
-        <v>19.39077673076099</v>
+        <v>3.151001218748661</v>
       </c>
       <c r="E10" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F10" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>9.842763498953847</v>
+        <v>1.59944906858</v>
       </c>
       <c r="D11" t="n">
-        <v>23.44335918448138</v>
+        <v>3.809545867478224</v>
       </c>
       <c r="E11" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F11" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.78926795102464</v>
+        <v>3.215756042041504</v>
       </c>
       <c r="D12" t="n">
-        <v>33.39409029144316</v>
+        <v>5.426539672359514</v>
       </c>
       <c r="E12" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F12" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>6.993433325164168</v>
+        <v>1.136432915339177</v>
       </c>
       <c r="D13" t="n">
-        <v>13.34140155484803</v>
+        <v>2.167977752662805</v>
       </c>
       <c r="E13" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F13" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>6.213935672586672</v>
+        <v>1.009764546795334</v>
       </c>
       <c r="D14" t="n">
-        <v>8.144225252538298</v>
+        <v>1.323436603537474</v>
       </c>
       <c r="E14" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F14" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>13.92044652871797</v>
+        <v>2.26207256091667</v>
       </c>
       <c r="D15" t="n">
-        <v>16.88897492592991</v>
+        <v>2.744458425463611</v>
       </c>
       <c r="E15" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F15" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>13.95018083633566</v>
+        <v>2.266904385904545</v>
       </c>
       <c r="D16" t="n">
-        <v>12.40515343880981</v>
+        <v>2.015837433806594</v>
       </c>
       <c r="E16" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F16" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>16.440885141984</v>
+        <v>2.671643835572401</v>
       </c>
       <c r="D17" t="n">
-        <v>24.34542067338746</v>
+        <v>3.956130859425463</v>
       </c>
       <c r="E17" t="n">
-        <v>8.964289098704377</v>
+        <v>1.456696978539461</v>
       </c>
       <c r="F17" t="n">
-        <v>8.379705862519438</v>
+        <v>1.361702202659409</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
